--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,6 +260,12 @@
     <t>TOTAL CHARGE (-.07)</t>
   </si>
   <si>
+    <t>IntegratedBillingAction350.arBillNumber</t>
+  </si>
+  <si>
+    <t>AR BILL NUMBER (-.11)</t>
+  </si>
+  <si>
     <t>IntegratedBillingAction350.dateEntryAdded</t>
   </si>
   <si>
@@ -274,12 +280,6 @@
   </si>
   <si>
     <t>ACTION TYPE (-.03)</t>
-  </si>
-  <si>
-    <t>IntegratedBillingAction350.arBillNumber</t>
-  </si>
-  <si>
-    <t>AR BILL NUMBER (-.11)</t>
   </si>
   <si>
     <t>IntegratedBillingAction350.patient</t>
@@ -1077,13 +1077,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="L5" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="M5" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1177,7 +1177,7 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>87</v>
@@ -1234,7 +1234,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -260,12 +260,6 @@
     <t>TOTAL CHARGE (-.07)</t>
   </si>
   <si>
-    <t>IntegratedBillingAction350.arBillNumber</t>
-  </si>
-  <si>
-    <t>AR BILL NUMBER (-.11)</t>
-  </si>
-  <si>
     <t>IntegratedBillingAction350.dateEntryAdded</t>
   </si>
   <si>
@@ -280,6 +274,12 @@
   </si>
   <si>
     <t>ACTION TYPE (-.03)</t>
+  </si>
+  <si>
+    <t>IntegratedBillingAction350.arBillNumber</t>
+  </si>
+  <si>
+    <t>AR BILL NUMBER (-.11)</t>
   </si>
   <si>
     <t>IntegratedBillingAction350.patient</t>
@@ -1077,13 +1077,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1177,7 +1177,7 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="L6" t="s" s="2">
         <v>87</v>
@@ -1234,7 +1234,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="96">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,17 @@
     <t>IntegratedBillingAction350.actionType</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/IbActionTypes3501)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/IbActionType3501)
 </t>
   </si>
   <si>
     <t>ACTION TYPE (-.03)</t>
+  </si>
+  <si>
+    <t>IntegratedBillingAction350.cancellationReason</t>
+  </si>
+  <si>
+    <t>CANCELLATION REASON (-.1)</t>
   </si>
   <si>
     <t>IntegratedBillingAction350.arBillNumber</t>
@@ -599,11 +605,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ9"/>
+  <dimension ref="A1:AJ10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.0078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.0078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.96875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.96875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
@@ -612,7 +618,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="63.57421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="62.6171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -633,7 +639,7 @@
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="43.96875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1549,6 +1555,106 @@
         <v>72</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-IntegratedBillingAction350.xlsx
+++ b/docs/StructureDefinition-IntegratedBillingAction350.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
